--- a/Frahm_etal_1982/Frahm_etal_1982_Table2_snapshot.xlsx
+++ b/Frahm_etal_1982/Frahm_etal_1982_Table2_snapshot.xlsx
@@ -1,45 +1,227 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/Frahm_etal_1982/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_62221CDD730045B148EEFB087053249725C85B5D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB74971B-166C-E44D-859E-A8ACFDFC7BAF}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="36920" yWindow="-1420" windowWidth="34560" windowHeight="20260" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="50560" yWindow="-4960" windowWidth="19900" windowHeight="23760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table2" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Table2" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+  <si>
+    <t>Table 2. Volumes and percentages of total neocortex, white and grey matters, and laminae 1 and 2–6 in Insectivora, Scandentia, and Primates¹</t>
+  </si>
+  <si>
+    <t>species</t>
+  </si>
+  <si>
+    <t>total neocortex in mm³</t>
+  </si>
+  <si>
+    <t>white matter in mm³</t>
+  </si>
+  <si>
+    <t>white matter in % of neocortex</t>
+  </si>
+  <si>
+    <t>grey matter in mm³</t>
+  </si>
+  <si>
+    <t>lam 1 in mm³</t>
+  </si>
+  <si>
+    <t>lam 1 in % of grey matter</t>
+  </si>
+  <si>
+    <t>lam 2–6 in mm³</t>
+  </si>
+  <si>
+    <t>(1)</t>
+  </si>
+  <si>
+    <t>(2)</t>
+  </si>
+  <si>
+    <t>(3)</t>
+  </si>
+  <si>
+    <t>(4)</t>
+  </si>
+  <si>
+    <t>(5)</t>
+  </si>
+  <si>
+    <t>(6)</t>
+  </si>
+  <si>
+    <t>(7)</t>
+  </si>
+  <si>
+    <t>Tenrec ecaudatus</t>
+  </si>
+  <si>
+    <t>Setifer setosus</t>
+  </si>
+  <si>
+    <t>Hemicentetes semispinosus</t>
+  </si>
+  <si>
+    <t>Echinops telfairi</t>
+  </si>
+  <si>
+    <t>Erinaceus algirus</t>
+  </si>
+  <si>
+    <t>Erinaceus europaeus</t>
+  </si>
+  <si>
+    <t>Hemiechinus auritus</t>
+  </si>
+  <si>
+    <t>Crocidura flavescens</t>
+  </si>
+  <si>
+    <t>Crocidura russula</t>
+  </si>
+  <si>
+    <t>Suncus murinus</t>
+  </si>
+  <si>
+    <t>Sorex araneus</t>
+  </si>
+  <si>
+    <t>Sorex minutus</t>
+  </si>
+  <si>
+    <t>Neomys fodiens</t>
+  </si>
+  <si>
+    <t>Tupaia glis (2)</t>
+  </si>
+  <si>
+    <t>Urogale everetti</t>
+  </si>
+  <si>
+    <t>Microcebus murinus (4)</t>
+  </si>
+  <si>
+    <t>Lemur albifrons</t>
+  </si>
+  <si>
+    <t>Lepilemur ruficaudatus</t>
+  </si>
+  <si>
+    <t>Avahi laniger occidentalis</t>
+  </si>
+  <si>
+    <t>Propithecus verreauxi (2)</t>
+  </si>
+  <si>
+    <t>Indri indri</t>
+  </si>
+  <si>
+    <t>Daubentonia madagascar.</t>
+  </si>
+  <si>
+    <t>Nycticebus coucang</t>
+  </si>
+  <si>
+    <t>Galagoides demidoff</t>
+  </si>
+  <si>
+    <t>Tarsius sp.</t>
+  </si>
+  <si>
+    <t>Callithrix jacchus</t>
+  </si>
+  <si>
+    <t>Cebuella pygmaea</t>
+  </si>
+  <si>
+    <t>Cebus sp.</t>
+  </si>
+  <si>
+    <t>Aotus trivirgatus</t>
+  </si>
+  <si>
+    <t>Saimiri sciureus</t>
+  </si>
+  <si>
+    <t>Alouatta sp.</t>
+  </si>
+  <si>
+    <t>Lagothrix lagothricha</t>
+  </si>
+  <si>
+    <t>Papio anubis</t>
+  </si>
+  <si>
+    <t>Cercopithecus ascanius</t>
+  </si>
+  <si>
+    <t>Colobus badius</t>
+  </si>
+  <si>
+    <t>Hylobates lar</t>
+  </si>
+  <si>
+    <t>Pan troglodytes</t>
+  </si>
+  <si>
+    <t>Homo sapiens</t>
+  </si>
+  <si>
+    <t>¹ Percentage values of the grey matter complement those of the white matter, percentage values of layers 2–6 complement those of layer 1. In both cases they sum to 100 and are not given. If more than one individual is measured, the number of specimens is given in brackets behind the species name.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -58,91 +240,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -430,1174 +553,1060 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="26" customWidth="1" style="5" min="1" max="1"/>
-    <col width="11" customWidth="1" style="5" min="2" max="8"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Table 2. Volumes and percentages of total neocortex, white and grey matters, and laminae 1 and 2–6 in Insectivora, Scandentia, and Primates¹</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="48" customHeight="1" s="5">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>species</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>total neocortex in mm³</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>white matter in mm³</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>white matter in % of neocortex</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>grey matter in mm³</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>lam 1 in mm³</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>lam 1 in % of grey matter</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>lam 2–6 in mm³</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1" s="5">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>(1)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>(3)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>(4)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>(5)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>(6)</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>(7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Tenrec ecaudatus</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>270.9</v>
-      </c>
-      <c r="C5" t="n">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>270.89999999999998</v>
+      </c>
+      <c r="C5">
         <v>35.51</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>13.1</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>235.4</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>72.81</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>30.9</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>162.5</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Setifer setosus</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
         <v>134.1</v>
       </c>
-      <c r="C6" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="C6">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="D6">
         <v>13</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>116.7</v>
       </c>
-      <c r="F6" t="n">
-        <v>37.48</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="F6">
+        <v>37.479999999999997</v>
+      </c>
+      <c r="G6">
         <v>32.1</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>79.23</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Hemicentetes semispinosus</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>73.43000000000001</v>
-      </c>
-      <c r="C7" t="n">
-        <v>5.865</v>
-      </c>
-      <c r="D7" t="n">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <v>73.430000000000007</v>
+      </c>
+      <c r="C7">
+        <v>5.8650000000000002</v>
+      </c>
+      <c r="D7">
         <v>8</v>
       </c>
-      <c r="E7" t="n">
-        <v>67.56999999999999</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="E7">
+        <v>67.569999999999993</v>
+      </c>
+      <c r="F7">
         <v>22.94</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>33.9</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>44.63</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Echinops telfairi</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
         <v>51.46</v>
       </c>
-      <c r="C8" t="n">
-        <v>5.224</v>
-      </c>
-      <c r="D8" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="C8">
+        <v>5.2240000000000002</v>
+      </c>
+      <c r="D8">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E8">
         <v>46.23</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>15.25</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>33</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>30.98</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Erinaceus algirus</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10">
         <v>500.3</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>63.6</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>12.7</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>436.7</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>117</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>26.8</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>319.7</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Erinaceus europaeus</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11">
         <v>522.5</v>
       </c>
-      <c r="C11" t="n">
-        <v>68.34999999999999</v>
-      </c>
-      <c r="D11" t="n">
+      <c r="C11">
+        <v>68.349999999999994</v>
+      </c>
+      <c r="D11">
         <v>13.1</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>454.1</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>129.1</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>28.4</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>325</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Hemiechinus auritus</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12">
         <v>309.5</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>30.8</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>10</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>278.7</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>75.03</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>26.9</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>203.7</v>
       </c>
     </row>
-    <row r="14" s="5">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Crocidura flavescens</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14">
         <v>59.11</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>4.99</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>8.4</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>54.12</v>
       </c>
-      <c r="F14" t="n">
-        <v>16.15</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="F14">
+        <v>16.149999999999999</v>
+      </c>
+      <c r="G14">
         <v>29.8</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>37.97</v>
       </c>
     </row>
-    <row r="15" s="5">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Crocidura russula</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15">
         <v>25.46</v>
       </c>
-      <c r="C15" t="n">
-        <v>1.487</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="C15">
+        <v>1.4870000000000001</v>
+      </c>
+      <c r="D15">
         <v>5.8</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>23.98</v>
       </c>
-      <c r="F15" t="n">
-        <v>6.872</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="F15">
+        <v>6.8719999999999999</v>
+      </c>
+      <c r="G15">
         <v>28.7</v>
       </c>
-      <c r="H15" t="n">
-        <v>17.1</v>
-      </c>
-    </row>
-    <row r="16" s="5">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Suncus murinus</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+      <c r="H15">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16">
         <v>54.13</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>3.54</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>6.5</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>50.59</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>14.07</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>27.8</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>36.51</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Sorex araneus</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17">
         <v>26.36</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>1.536</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>5.8</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>24.82</v>
       </c>
-      <c r="F17" t="n">
-        <v>5.189</v>
-      </c>
-      <c r="G17" t="n">
+      <c r="F17">
+        <v>5.1890000000000001</v>
+      </c>
+      <c r="G17">
         <v>20.9</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>19.63</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Sorex minutus</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18">
         <v>12.65</v>
       </c>
-      <c r="C18" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="D18" t="n">
+      <c r="C18">
+        <v>0.84399999999999997</v>
+      </c>
+      <c r="D18">
         <v>6.7</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>11.81</v>
       </c>
-      <c r="F18" t="n">
-        <v>2.436</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="F18">
+        <v>2.4359999999999999</v>
+      </c>
+      <c r="G18">
         <v>20.6</v>
       </c>
-      <c r="H18" t="n">
-        <v>9.371</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Neomys fodiens</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
+      <c r="H18">
+        <v>9.3710000000000004</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19">
         <v>56.56</v>
       </c>
-      <c r="C19" t="n">
-        <v>6.371</v>
-      </c>
-      <c r="D19" t="n">
+      <c r="C19">
+        <v>6.3710000000000004</v>
+      </c>
+      <c r="D19">
         <v>11.3</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>50.19</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>9.67</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>19.3</v>
       </c>
-      <c r="H19" t="n">
-        <v>40.52</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Tupaia glis (2)</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
+      <c r="H19">
+        <v>40.520000000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21">
         <v>1036</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>94.83</v>
       </c>
-      <c r="D21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E21" t="n">
+      <c r="D21">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E21">
         <v>941.4</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>126.8</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>13.5</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>814.6</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Urogale everetti</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22">
         <v>1338</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>199.2</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>14.9</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>1139</v>
       </c>
-      <c r="F22" t="n">
-        <v>157.2</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="F22">
+        <v>157.19999999999999</v>
+      </c>
+      <c r="G22">
         <v>13.8</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22">
         <v>981.6</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Microcebus murinus (4)</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24">
         <v>739.5</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>65.31</v>
       </c>
-      <c r="D24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="E24" t="n">
+      <c r="D24">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E24">
         <v>674.2</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>94.97</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>14.1</v>
       </c>
-      <c r="H24" t="n">
-        <v>579.3</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Lemur albifrons</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
+      <c r="H24">
+        <v>579.29999999999995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25">
         <v>12207</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>3035</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>24.9</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>9172</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>1298</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>14.2</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>7874</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Lepilemur ruficaudatus</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26">
         <v>3282</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>476.6</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>14.5</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>2805</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>488.6</v>
       </c>
-      <c r="G26" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="H26" t="n">
+      <c r="G26">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="H26">
         <v>2317</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Avahi laniger occidentalis</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="5">
         <v>4443</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>777</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>17.5</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>3666</v>
       </c>
-      <c r="F27" t="n">
-        <v>582.7</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="F27">
+        <v>582.70000000000005</v>
+      </c>
+      <c r="G27">
         <v>15.9</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27">
         <v>3083</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Propithecus verreauxi (2)</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28">
         <v>13170</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>3335</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>25.3</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>9835</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>1428</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28">
         <v>14.5</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28">
         <v>8407</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Indri indri</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29">
         <v>20114</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>4223</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>21</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>15891</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>2702</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29">
         <v>17</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29">
         <v>13189</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Daubentonia madagascar.</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30">
         <v>22127</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>5053</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>22.8</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30">
         <v>17074</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>2738</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30">
         <v>16</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30">
         <v>14336</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Nycticebus coucang</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31">
         <v>6192</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>1240</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>20</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>4952</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>712.7</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31">
         <v>14.4</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31">
         <v>4240</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Galagoides demidoff</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32">
         <v>1568</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>150.6</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>9.6</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32">
         <v>1417</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32">
         <v>202.2</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32">
         <v>14.3</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32">
         <v>1215</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Tarsius sp.</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33">
         <v>1768</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>137</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>7.7</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33">
         <v>1631</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33">
         <v>236.3</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33">
         <v>14.5</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33">
         <v>1395</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Callithrix jacchus</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35">
         <v>4371</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>807.1</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>18.5</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35">
         <v>3564</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35">
         <v>441.8</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35">
         <v>12.4</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H35">
         <v>3122</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Cebuella pygmaea</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36">
         <v>2534</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>395.3</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>15.6</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>2139</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36">
         <v>223.7</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36">
         <v>10.5</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36">
         <v>1915</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Cebus sp.</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37">
         <v>46429</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>15799</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>34</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37">
         <v>30630</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37">
         <v>3607</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G37">
         <v>11.8</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H37">
         <v>27023</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Aotus trivirgatus</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="5">
         <v>9950</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>2174</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38">
         <v>21.8</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38">
         <v>7776</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38">
         <v>1039</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38">
         <v>13.4</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H38">
         <v>6737</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39">
         <v>15541</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>3710</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>23.9</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39">
         <v>11832</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39">
         <v>1275</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39">
         <v>10.8</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H39">
         <v>10557</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Alouatta sp.</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40">
         <v>31660</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>9869</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40">
         <v>31.2</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40">
         <v>21791</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40">
         <v>2918</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40">
         <v>13.4</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H40">
         <v>18874</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Lagothrix lagothricha</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41">
         <v>65873</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41">
         <v>16727</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>25.4</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41">
         <v>49147</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41">
         <v>7664</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G41">
         <v>15.6</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H41">
         <v>41483</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Papio anubis</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43">
         <v>140142</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43">
         <v>54416</v>
       </c>
-      <c r="D43" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="E43" t="n">
+      <c r="D43">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="E43">
         <v>85726</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43">
         <v>10642</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43">
         <v>12.4</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H43">
         <v>75084</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Cercopithecus ascanius</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44">
         <v>45166</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>13052</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>28.9</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44">
         <v>32114</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44">
         <v>4009</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44">
         <v>12.5</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H44">
         <v>28104</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Colobus badius</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45">
         <v>50906</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45">
         <v>14331</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45">
         <v>28.2</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45">
         <v>36575</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45">
         <v>5130</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G45">
         <v>14</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H45">
         <v>31444</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Hylobates lar</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="5">
         <v>65800</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>19154</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47">
         <v>29.1</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47">
         <v>46646</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47">
         <v>6279</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G47">
         <v>13.5</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H47">
         <v>40367</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="5">
         <v>291592</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48">
         <v>118996</v>
       </c>
-      <c r="D48" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="E48" t="n">
+      <c r="D48">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="E48">
         <v>172597</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48">
         <v>21960</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G48">
         <v>12.7</v>
       </c>
-      <c r="H48" t="n">
+      <c r="H48">
         <v>150637</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50">
         <v>1006525</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50">
         <v>421819</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50">
         <v>41.9</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50">
         <v>584706</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50">
         <v>75316</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G50">
         <v>12.9</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H50">
         <v>509391</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>¹ Percentage values of the grey matter complement those of the white matter, percentage values of layers 2–6 complement those of layer 1. In both cases they sum to 100 and are not given. If more than one individual is measured, the number of specimens is given in brackets behind the species name.</t>
-        </is>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1606,6 +1615,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -1860,34 +1889,46 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7BF4A5C-195D-4C15-ACB2-79AAD01BA061}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B2438FA-A772-404E-9503-813A3A1E1207}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{186AA5F8-4C77-43CF-A794-1681271B9A69}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{186AA5F8-4C77-43CF-A794-1681271B9A69}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B2438FA-A772-404E-9503-813A3A1E1207}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7BF4A5C-195D-4C15-ACB2-79AAD01BA061}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>